--- a/tests/data/LoginData.xlsx
+++ b/tests/data/LoginData.xlsx
@@ -3,6 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+  <bookViews>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
+  </bookViews>
   <sheets>
     <sheet sheetId="1" name="login Data" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="login Data2" state="visible" r:id="rId5"/>
@@ -13,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="97">
   <si>
     <t>email</t>
   </si>
@@ -184,9 +187,6 @@
   </si>
   <si>
     <t>SuperSecretPassword!17</t>
-  </si>
-  <si>
-    <t>You logged into a secure area!18</t>
   </si>
   <si>
     <t>email9</t>
@@ -322,8 +322,9 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <color theme="1"/>
-      <scheme val="minor"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
+      <sz val="11"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -347,10 +348,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment readingOrder="1"/>
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -370,14 +375,14 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Sheets">
+    <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
@@ -404,22 +409,82 @@
         <a:srgbClr val="46BDC6"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Sheets">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -431,623 +496,686 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:tint val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="9500"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot rev="0" lon="0" lat="0"/>
+            </a:camera>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:tint val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:D15"/>
-  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="12.63" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="30.63" customWidth="1"/>
-    <col min="3" max="3" width="34.13" customWidth="1"/>
+    <col min="1" max="1" width="12.43357142857143" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.576428571428572" style="1" customWidth="1"/>
+    <col min="3" max="3" width="34.14785714285715" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.43357142857143" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="2" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="C2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="C3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="C4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="2"/>
+    </row>
+    <row r="5" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="C5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="C6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="C7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+    <row r="8" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="C8" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="C9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="C10" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="11" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="C11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="C12" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="C13" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="2"/>
+    </row>
+    <row r="14" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="C14" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="2"/>
+    </row>
+    <row r="15" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="C15" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="2"/>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:E19"/>
-  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="12.63" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="31.13" customWidth="1"/>
-    <col min="4" max="4" width="34" customWidth="1"/>
+    <col min="1" max="2" width="12.43357142857143" style="1" customWidth="1"/>
+    <col min="3" max="3" width="31.14785714285714" style="1" customWidth="1"/>
+    <col min="4" max="4" width="34.005" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.43357142857143" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="2" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="3" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="3" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="3" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+    <row r="8" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="3" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="3"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="B10" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="B11" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="B12" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="C12" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="D12" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="B13" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="C13" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="B14" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="C14" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="D14" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="B15" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="C15" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="D15" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="B16" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="C16" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="D16" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+      <c r="B17" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="C17" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="D17" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+      <c r="B18" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="C18" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="D18" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+      <c r="B19" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="C19" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="D19" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>97</v>
-      </c>
+      <c r="E19" s="2"/>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:A1"/>
-  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="12.63" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/tests/data/LoginData.xlsx
+++ b/tests/data/LoginData.xlsx
@@ -348,12 +348,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -668,192 +667,179 @@
     <col min="1" max="1" width="12.43357142857143" style="1" customWidth="1"/>
     <col min="2" max="2" width="30.576428571428572" style="1" customWidth="1"/>
     <col min="3" max="3" width="34.14785714285715" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.43357142857143" style="2" customWidth="1"/>
+    <col min="4" max="4" width="12.43357142857143" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+    <row r="2" ht="17.25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="2"/>
-    </row>
-    <row r="3" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="C2" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" ht="17.25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="2"/>
-    </row>
-    <row r="4" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="C3" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" ht="17.25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="2"/>
-    </row>
-    <row r="5" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="C4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" ht="17.25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="2"/>
-    </row>
-    <row r="6" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="C5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" ht="17.25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="2"/>
+      <c r="C6" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="7" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="C7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+    <row r="8" ht="17.25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="2"/>
-    </row>
-    <row r="9" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="C8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" ht="17.25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="2"/>
-    </row>
-    <row r="10" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="C9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" ht="17.25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="11" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="C10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" ht="17.25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="2"/>
-    </row>
-    <row r="12" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="C11" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" ht="17.25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" s="2"/>
-    </row>
-    <row r="13" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="C12" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" ht="17.25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D13" s="2"/>
-    </row>
-    <row r="14" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="C13" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" ht="17.25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14" s="2"/>
-    </row>
-    <row r="15" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="C14" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" ht="17.25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="2"/>
+      <c r="C15" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -871,297 +857,281 @@
     <col min="1" max="2" width="12.43357142857143" style="1" customWidth="1"/>
     <col min="3" max="3" width="31.14785714285714" style="1" customWidth="1"/>
     <col min="4" max="4" width="34.005" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.43357142857143" style="2" customWidth="1"/>
+    <col min="5" max="5" width="12.43357142857143" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+    <row r="3" ht="18.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E3" s="2"/>
-    </row>
-    <row r="4" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+    </row>
+    <row r="4" ht="18.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E4" s="2"/>
-    </row>
-    <row r="5" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+    </row>
+    <row r="5" ht="18.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+    </row>
+    <row r="6" ht="18.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E6" s="2"/>
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+    <row r="8" ht="18.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+    </row>
+    <row r="9" ht="18.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10" ht="18.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+    </row>
+    <row r="11" ht="18.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+    </row>
+    <row r="12" ht="18.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+    </row>
+    <row r="13" ht="18.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+    </row>
+    <row r="14" ht="18.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E14" s="2"/>
-    </row>
-    <row r="15" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+    </row>
+    <row r="15" ht="18.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E15" s="2"/>
-    </row>
-    <row r="16" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+    </row>
+    <row r="16" ht="18.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+    </row>
+    <row r="17" ht="18.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+    </row>
+    <row r="18" ht="18.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="E18" s="2"/>
-    </row>
-    <row r="19" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+    </row>
+    <row r="19" ht="18.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="E19" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
